--- a/Prices.xlsx
+++ b/Prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/an-chilu/Desktop/Career/Past Projects/Electricity Plant Power Optimization/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/an-chilu/Desktop/Career/Past Projects/Energy-Plant-Optimization-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C8B383-305C-D94D-8A7A-FDC664DD883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEA2C50-4461-4E4A-9A1F-5BE5D4583553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1500" windowWidth="14380" windowHeight="12460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13540" yWindow="880" windowWidth="14380" windowHeight="12460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRICE_ELECTRIC" sheetId="4" r:id="rId1"/>
@@ -2864,6 +2864,11 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="2613f182-e424-487f-ac7f-33bed2fc986a">
@@ -2940,11 +2945,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1666D2F8-1E58-4FCD-8367-B6E0CC4C51A9}">
   <ds:schemaRefs>
@@ -2965,6 +2965,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{569AA5FB-642C-4FF8-A162-81A7B3EA3312}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF84784E-56B2-46F5-B48A-7785015432C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2973,12 +2981,4 @@
     <ds:schemaRef ds:uri="5bcbeff6-7c02-4b0f-b125-f1b3d566cc14"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{569AA5FB-642C-4FF8-A162-81A7B3EA3312}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>